--- a/ПР3/Диски в нодах.xlsx
+++ b/ПР3/Диски в нодах.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Mirea\Системы хранения данных\ПР3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F46E37-8279-484E-813B-4E203DCAE5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EA224E-7685-403E-AF6F-BD9ED81B9784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{F74CFAD6-B332-42FB-B9FC-56C5254BE587}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{F74CFAD6-B332-42FB-B9FC-56C5254BE587}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
-    <t>Объем данных с резервированием, Тб</t>
-  </si>
-  <si>
     <t>Объем одного диска, Тб</t>
   </si>
   <si>
@@ -93,6 +90,9 @@
   </si>
   <si>
     <t>Объем с фактором репликации</t>
+  </si>
+  <si>
+    <t>Объем данных с реплицией, Тб</t>
   </si>
 </sst>
 </file>
@@ -193,7 +193,7 @@
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{7533D3A0-5137-4C4F-854A-7A1E130BDAC2}" name="Объем одного диска, Тб" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{F8C5EF21-07E4-40FC-BB2A-F88B4CEE11ED}" name="Макс. Дисков на ноде"/>
-    <tableColumn id="3" xr3:uid="{42F1D319-2C90-4B08-B833-C2C2C267B5B0}" name="Объем данных с резервированием, Тб">
+    <tableColumn id="3" xr3:uid="{42F1D319-2C90-4B08-B833-C2C2C267B5B0}" name="Объем данных с реплицией, Тб">
       <calculatedColumnFormula>$R$4+2*A2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{577C7AF6-AD21-4931-8D7C-3407905F1FC2}" name="Кол-во дисков, разн." dataDxfId="9">
@@ -549,70 +549,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9271E5F6-9FD8-473F-AB62-FF61DD1AE32B}">
-  <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.453125" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1796875" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.21875" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>6.4</v>
       </c>
@@ -621,15 +625,15 @@
       </c>
       <c r="C2">
         <f t="shared" ref="C2:C9" si="0">$R$4+2*A2</f>
-        <v>51.8</v>
+        <v>267.8</v>
       </c>
       <c r="D2">
         <f t="shared" ref="D2:D9" si="1">_xlfn.CEILING.MATH(C2/A2)</f>
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E2">
         <f>MAX($O$4,_xlfn.CEILING.MATH(Таблица1[[#This Row],[Кол-во дисков, разн.]]/Таблица1[[#This Row],[Макс. Дисков на ноде]]))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
         <f>217492</f>
@@ -637,37 +641,37 @@
       </c>
       <c r="G2">
         <f>QUOTIENT(D2,Таблица1[[#This Row],[Количество нод]]) + _xlfn.CEILING.MATH(MOD(INT(D2),Таблица1[[#This Row],[Количество нод]])/Таблица1[[#This Row],[Количество нод]])</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <f>Таблица1[[#This Row],[Количество дисков на 1 ноде]]*Таблица1[[#This Row],[Количество нод]]*Таблица1[[#This Row],[Объем одного диска, Тб]]</f>
-        <v>57.6</v>
+        <v>288</v>
       </c>
       <c r="I2" s="2">
         <f t="shared" ref="I2:I9" si="2">F2*G2</f>
-        <v>652476</v>
+        <v>1957428</v>
       </c>
       <c r="J2" s="2">
         <f>I2*Таблица1[[#This Row],[Количество нод]]</f>
-        <v>1957428</v>
+        <v>9787140</v>
       </c>
       <c r="K2" s="2">
         <v>200000</v>
       </c>
       <c r="L2" s="2">
         <f>Таблица1[[#This Row],[Количество нод]]*Таблица1[[#This Row],[Соимость 1 ноды]]</f>
-        <v>600000</v>
+        <v>1000000</v>
       </c>
       <c r="M2" s="2">
         <f>Таблица1[[#This Row],[Цена всех дисков]]+Таблица1[[#This Row],[Стоимость всех нод]]</f>
-        <v>2557428</v>
+        <v>10787140</v>
       </c>
       <c r="N2" s="2">
         <f>Таблица1[[#This Row],[Общ]]/Таблица1[[#This Row],[Итоговая ёмкость]]</f>
-        <v>44399.791666666664</v>
+        <v>37455.347222222219</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2.4</v>
       </c>
@@ -675,65 +679,65 @@
         <v>26</v>
       </c>
       <c r="C3">
-        <f t="shared" si="0"/>
-        <v>43.8</v>
+        <f>$R$4+2*A3</f>
+        <v>259.8</v>
       </c>
       <c r="D3">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="E3">
         <f>MAX($O$4,_xlfn.CEILING.MATH(Таблица1[[#This Row],[Кол-во дисков, разн.]]/Таблица1[[#This Row],[Макс. Дисков на ноде]]))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
         <v>5526</v>
       </c>
       <c r="G3">
         <f>QUOTIENT(D3,Таблица1[[#This Row],[Количество нод]]) + _xlfn.CEILING.MATH(MOD(INT(D3),Таблица1[[#This Row],[Количество нод]])/Таблица1[[#This Row],[Количество нод]])</f>
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H3">
         <f>Таблица1[[#This Row],[Количество дисков на 1 ноде]]*Таблица1[[#This Row],[Количество нод]]*Таблица1[[#This Row],[Объем одного диска, Тб]]</f>
-        <v>50.4</v>
+        <v>264</v>
       </c>
       <c r="I3" s="2">
         <f t="shared" si="2"/>
-        <v>38682</v>
+        <v>121572</v>
       </c>
       <c r="J3" s="2">
         <f>I3*Таблица1[[#This Row],[Количество нод]]</f>
-        <v>116046</v>
+        <v>607860</v>
       </c>
       <c r="K3" s="2">
         <v>300000</v>
       </c>
       <c r="L3" s="2">
         <f>Таблица1[[#This Row],[Количество нод]]*Таблица1[[#This Row],[Соимость 1 ноды]]</f>
-        <v>900000</v>
+        <v>1500000</v>
       </c>
       <c r="M3" s="2">
         <f>Таблица1[[#This Row],[Цена всех дисков]]+Таблица1[[#This Row],[Стоимость всех нод]]</f>
-        <v>1016046</v>
+        <v>2107860</v>
       </c>
       <c r="N3" s="2">
         <f>Таблица1[[#This Row],[Общ]]/Таблица1[[#This Row],[Итоговая ёмкость]]</f>
-        <v>20159.642857142859</v>
+        <v>7984.318181818182</v>
       </c>
       <c r="O3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="s">
         <v>9</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" t="s">
-        <v>10</v>
-      </c>
-      <c r="R3" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>14</v>
       </c>
@@ -742,11 +746,11 @@
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
-        <v>67</v>
+        <v>283</v>
       </c>
       <c r="D4">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <f>MAX($O$4,_xlfn.CEILING.MATH(Таблица1[[#This Row],[Кол-во дисков, разн.]]/Таблица1[[#This Row],[Макс. Дисков на ноде]]))</f>
@@ -757,19 +761,19 @@
       </c>
       <c r="G4">
         <f>QUOTIENT(D4,Таблица1[[#This Row],[Количество нод]]) + _xlfn.CEILING.MATH(MOD(INT(D4),Таблица1[[#This Row],[Количество нод]])/Таблица1[[#This Row],[Количество нод]])</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H4">
         <f>Таблица1[[#This Row],[Количество дисков на 1 ноде]]*Таблица1[[#This Row],[Количество нод]]*Таблица1[[#This Row],[Объем одного диска, Тб]]</f>
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="I4" s="2">
         <f t="shared" si="2"/>
-        <v>99312</v>
+        <v>347592</v>
       </c>
       <c r="J4" s="2">
         <f>I4*Таблица1[[#This Row],[Количество нод]]</f>
-        <v>297936</v>
+        <v>1042776</v>
       </c>
       <c r="K4" s="2">
         <v>300000</v>
@@ -780,27 +784,27 @@
       </c>
       <c r="M4" s="2">
         <f>Таблица1[[#This Row],[Цена всех дисков]]+Таблица1[[#This Row],[Стоимость всех нод]]</f>
-        <v>1197936</v>
+        <v>1942776</v>
       </c>
       <c r="N4" s="2">
         <f>Таблица1[[#This Row],[Общ]]/Таблица1[[#This Row],[Итоговая ёмкость]]</f>
-        <v>14261.142857142857</v>
+        <v>6608.0816326530612</v>
       </c>
       <c r="O4">
         <v>3</v>
       </c>
       <c r="P4">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="Q4">
         <v>3</v>
       </c>
       <c r="R4">
         <f>P4*Q4</f>
-        <v>39</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>24</v>
       </c>
@@ -809,11 +813,11 @@
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="D5">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <f>MAX($O$4,_xlfn.CEILING.MATH(Таблица1[[#This Row],[Кол-во дисков, разн.]]/Таблица1[[#This Row],[Макс. Дисков на ноде]]))</f>
@@ -824,19 +828,19 @@
       </c>
       <c r="G5">
         <f>QUOTIENT(D5,Таблица1[[#This Row],[Количество нод]]) + _xlfn.CEILING.MATH(MOD(INT(D5),Таблица1[[#This Row],[Количество нод]])/Таблица1[[#This Row],[Количество нод]])</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5">
         <f>Таблица1[[#This Row],[Количество дисков на 1 ноде]]*Таблица1[[#This Row],[Количество нод]]*Таблица1[[#This Row],[Объем одного диска, Тб]]</f>
-        <v>144</v>
+        <v>360</v>
       </c>
       <c r="I5" s="2">
         <f t="shared" si="2"/>
-        <v>194000</v>
+        <v>485000</v>
       </c>
       <c r="J5" s="2">
         <f>I5*Таблица1[[#This Row],[Количество нод]]</f>
-        <v>582000</v>
+        <v>1455000</v>
       </c>
       <c r="K5" s="2">
         <v>300000</v>
@@ -847,17 +851,17 @@
       </c>
       <c r="M5" s="2">
         <f>Таблица1[[#This Row],[Цена всех дисков]]+Таблица1[[#This Row],[Стоимость всех нод]]</f>
-        <v>1482000</v>
+        <v>2355000</v>
       </c>
       <c r="N5" s="2">
         <f>Таблица1[[#This Row],[Общ]]/Таблица1[[#This Row],[Итоговая ёмкость]]</f>
-        <v>10291.666666666666</v>
+        <v>6541.666666666667</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C6">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>255</v>
       </c>
       <c r="D6" t="e">
         <f t="shared" si="1"/>
@@ -900,10 +904,10 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>255</v>
       </c>
       <c r="D7" t="e">
         <f t="shared" si="1"/>
@@ -946,10 +950,10 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>255</v>
       </c>
       <c r="D8" t="e">
         <f t="shared" si="1"/>
@@ -992,10 +996,10 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>255</v>
       </c>
       <c r="D9" t="e">
         <f t="shared" si="1"/>
@@ -1038,10 +1042,21 @@
         <v>#DIV/0!</v>
       </c>
     </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="P13" s="2">
+        <f>AVERAGE(M3:M5)</f>
+        <v>2135212</v>
+      </c>
+      <c r="R13" s="2"/>
+    </row>
+    <row r="26" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L26" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>